--- a/Tresp_sem_outliers.xlsx
+++ b/Tresp_sem_outliers.xlsx
@@ -431,28 +431,34 @@
         </is>
       </c>
       <c r="C2">
-        <v>860</v>
+        <v>1128</v>
       </c>
       <c r="D2">
-        <v>680</v>
+        <v>1143.333333333333</v>
       </c>
       <c r="E2">
-        <v>670</v>
+        <v>1395</v>
       </c>
       <c r="F2">
-        <v>675</v>
-      </c>
-      <c r="G2">
-        <v>600</v>
+        <v>1347.5</v>
       </c>
       <c r="H2">
-        <v>600</v>
+        <v>1430</v>
+      </c>
+      <c r="I2">
+        <v>1430</v>
       </c>
       <c r="J2">
-        <v>675</v>
+        <v>1430</v>
+      </c>
+      <c r="K2">
+        <v>1430</v>
       </c>
       <c r="L2">
-        <v>610</v>
+        <v>1430</v>
+      </c>
+      <c r="M2">
+        <v>1430</v>
       </c>
     </row>
     <row r="3">
@@ -508,34 +514,37 @@
         </is>
       </c>
       <c r="C4">
-        <v>968</v>
+        <v>1115</v>
       </c>
       <c r="D4">
-        <v>1213.333333333333</v>
+        <v>1222</v>
       </c>
       <c r="E4">
-        <v>1133.333333333333</v>
+        <v>1136</v>
       </c>
       <c r="F4">
-        <v>1010</v>
+        <v>1220</v>
       </c>
       <c r="G4">
-        <v>950</v>
+        <v>1196.666666666667</v>
       </c>
       <c r="H4">
-        <v>725</v>
+        <v>1196.666666666667</v>
       </c>
       <c r="I4">
-        <v>1193.333333333333</v>
+        <v>1228.333333333333</v>
       </c>
       <c r="J4">
-        <v>1430</v>
+        <v>1285</v>
       </c>
       <c r="K4">
-        <v>720</v>
+        <v>1253.333333333333</v>
       </c>
       <c r="L4">
-        <v>1245</v>
+        <v>1128.333333333333</v>
+      </c>
+      <c r="M4">
+        <v>1231.666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -548,34 +557,37 @@
         </is>
       </c>
       <c r="C5">
-        <v>676.6666666666666</v>
+        <v>1430</v>
       </c>
       <c r="D5">
-        <v>1103.333333333333</v>
+        <v>1430</v>
       </c>
       <c r="E5">
-        <v>1376</v>
+        <v>1430</v>
       </c>
       <c r="F5">
-        <v>1327.5</v>
+        <v>1418</v>
       </c>
       <c r="G5">
-        <v>1232.5</v>
+        <v>1430</v>
       </c>
       <c r="H5">
         <v>1430</v>
       </c>
       <c r="I5">
-        <v>1055</v>
+        <v>1428</v>
       </c>
       <c r="J5">
+        <v>1380</v>
+      </c>
+      <c r="K5">
         <v>1430</v>
       </c>
       <c r="L5">
-        <v>695</v>
+        <v>1430</v>
       </c>
       <c r="M5">
-        <v>996.6666666666666</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="6">
@@ -674,34 +686,37 @@
         </is>
       </c>
       <c r="C8">
-        <v>930</v>
+        <v>690</v>
+      </c>
+      <c r="D8">
+        <v>750</v>
       </c>
       <c r="E8">
-        <v>760</v>
+        <v>805</v>
       </c>
       <c r="F8">
-        <v>740</v>
+        <v>606.6666666666666</v>
       </c>
       <c r="G8">
-        <v>726.6666666666666</v>
+        <v>680</v>
       </c>
       <c r="H8">
-        <v>630</v>
+        <v>676.6666666666666</v>
       </c>
       <c r="I8">
-        <v>694</v>
+        <v>682.5</v>
       </c>
       <c r="J8">
-        <v>595</v>
+        <v>692</v>
       </c>
       <c r="K8">
-        <v>1110</v>
+        <v>771.6666666666666</v>
       </c>
       <c r="L8">
-        <v>700</v>
+        <v>730</v>
       </c>
       <c r="M8">
-        <v>692.5</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="9">
@@ -714,34 +729,37 @@
         </is>
       </c>
       <c r="C9">
-        <v>1087.5</v>
+        <v>880</v>
       </c>
       <c r="D9">
-        <v>825</v>
+        <v>787.5</v>
+      </c>
+      <c r="E9">
+        <v>850</v>
       </c>
       <c r="F9">
-        <v>656</v>
+        <v>863.3333333333334</v>
       </c>
       <c r="G9">
-        <v>720</v>
+        <v>916</v>
       </c>
       <c r="H9">
-        <v>753.3333333333334</v>
+        <v>835</v>
       </c>
       <c r="I9">
-        <v>776</v>
+        <v>901.6666666666666</v>
       </c>
       <c r="J9">
-        <v>660</v>
+        <v>928.3333333333334</v>
       </c>
       <c r="K9">
-        <v>735</v>
+        <v>941.6666666666666</v>
       </c>
       <c r="L9">
-        <v>738</v>
+        <v>946</v>
       </c>
       <c r="M9">
-        <v>1002.5</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="10">
@@ -883,31 +901,37 @@
         </is>
       </c>
       <c r="C13">
-        <v>833.3333333333334</v>
+        <v>1018</v>
+      </c>
+      <c r="D13">
+        <v>1205</v>
       </c>
       <c r="E13">
-        <v>630</v>
+        <v>1180</v>
+      </c>
+      <c r="F13">
+        <v>1088.333333333333</v>
       </c>
       <c r="G13">
-        <v>605</v>
+        <v>1318</v>
       </c>
       <c r="H13">
-        <v>560</v>
+        <v>1218.333333333333</v>
       </c>
       <c r="I13">
-        <v>750</v>
+        <v>1338</v>
       </c>
       <c r="J13">
-        <v>845</v>
+        <v>1223.333333333333</v>
       </c>
       <c r="K13">
-        <v>820</v>
+        <v>1298</v>
       </c>
       <c r="L13">
-        <v>1030</v>
+        <v>1400</v>
       </c>
       <c r="M13">
-        <v>800</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="14">
@@ -963,37 +987,37 @@
         </is>
       </c>
       <c r="C15">
-        <v>1428</v>
+        <v>685</v>
       </c>
       <c r="D15">
-        <v>1156.666666666667</v>
+        <v>924</v>
       </c>
       <c r="E15">
-        <v>1343.333333333333</v>
+        <v>912</v>
       </c>
       <c r="F15">
-        <v>1161.666666666667</v>
+        <v>1028.333333333333</v>
       </c>
       <c r="G15">
-        <v>1116</v>
+        <v>918</v>
       </c>
       <c r="H15">
-        <v>1110</v>
+        <v>1133.333333333333</v>
       </c>
       <c r="I15">
-        <v>1086</v>
+        <v>1030</v>
       </c>
       <c r="J15">
-        <v>1004</v>
+        <v>1108.333333333333</v>
       </c>
       <c r="K15">
-        <v>1138.333333333333</v>
+        <v>1016</v>
       </c>
       <c r="L15">
-        <v>1083.333333333333</v>
+        <v>972.5</v>
       </c>
       <c r="M15">
-        <v>1073.333333333333</v>
+        <v>908</v>
       </c>
     </row>
     <row r="16">
@@ -1048,6 +1072,39 @@
           <t>GAG</t>
         </is>
       </c>
+      <c r="C17">
+        <v>782.5</v>
+      </c>
+      <c r="D17">
+        <v>652</v>
+      </c>
+      <c r="E17">
+        <v>780</v>
+      </c>
+      <c r="F17">
+        <v>830</v>
+      </c>
+      <c r="G17">
+        <v>970</v>
+      </c>
+      <c r="H17">
+        <v>886</v>
+      </c>
+      <c r="I17">
+        <v>886.6666666666666</v>
+      </c>
+      <c r="J17">
+        <v>940</v>
+      </c>
+      <c r="K17">
+        <v>816.6666666666666</v>
+      </c>
+      <c r="L17">
+        <v>875</v>
+      </c>
+      <c r="M17">
+        <v>822</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -1116,6 +1173,9 @@
       <c r="H19">
         <v>1218</v>
       </c>
+      <c r="I19">
+        <v>1426</v>
+      </c>
       <c r="J19">
         <v>1430</v>
       </c>
@@ -1743,6 +1803,18 @@
       <c r="F34">
         <v>1365</v>
       </c>
+      <c r="G34">
+        <v>1430</v>
+      </c>
+      <c r="H34">
+        <v>1430</v>
+      </c>
+      <c r="I34">
+        <v>1406.666666666667</v>
+      </c>
+      <c r="J34">
+        <v>1331.666666666667</v>
+      </c>
       <c r="K34">
         <v>794</v>
       </c>
@@ -1978,37 +2050,37 @@
         </is>
       </c>
       <c r="C40">
-        <v>825</v>
+        <v>926.6666666666666</v>
       </c>
       <c r="D40">
-        <v>708</v>
+        <v>955</v>
       </c>
       <c r="E40">
-        <v>710</v>
+        <v>1128.333333333333</v>
       </c>
       <c r="F40">
-        <v>641.6666666666666</v>
+        <v>1006</v>
       </c>
       <c r="G40">
-        <v>1035</v>
+        <v>1220</v>
       </c>
       <c r="H40">
-        <v>696</v>
+        <v>1278.333333333333</v>
       </c>
       <c r="I40">
-        <v>696.6666666666666</v>
+        <v>1293.333333333333</v>
       </c>
       <c r="J40">
-        <v>623.3333333333334</v>
+        <v>1296.666666666667</v>
       </c>
       <c r="K40">
-        <v>670</v>
+        <v>1061.666666666667</v>
       </c>
       <c r="L40">
-        <v>930</v>
+        <v>1178.333333333333</v>
       </c>
       <c r="M40">
-        <v>673.3333333333334</v>
+        <v>1128.333333333333</v>
       </c>
     </row>
     <row r="41">
